--- a/dokumentasi_black_box_testing.xlsx
+++ b/dokumentasi_black_box_testing.xlsx
@@ -3404,9 +3404,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3437,6 +3434,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3445,12 +3445,37 @@
     <dxf>
       <fill>
         <patternFill>
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -3463,6 +3488,213 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3487,6 +3719,29 @@
         <horizontal style="thin">
           <color rgb="FF000000"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -3744,261 +3999,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4013,31 +4013,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelSkenarioBlackBox" displayName="TabelSkenarioBlackBox" ref="A1:G144" headerRowDxfId="21" dataDxfId="20" totalsRowDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelSkenarioBlackBox" displayName="TabelSkenarioBlackBox" ref="A1:G144" headerRowDxfId="9" dataDxfId="8" totalsRowDxfId="7">
   <tableColumns count="7">
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ID Skenario" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Kebutuhan Fungsional" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Skenario Pengujian" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Prasyarat" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Data Uji" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Langkah Pengujian" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Ekspektasi Hasil" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ID Skenario" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Kebutuhan Fungsional" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Skenario Pengujian" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Prasyarat" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Data Uji" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Langkah Pengujian" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Ekspektasi Hasil" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{30CD9512-EB44-4CF4-9A36-02A1E4DC7CB1}" name="TabelSkenarioBlackBox4" displayName="TabelSkenarioBlackBox4" ref="A1:H145" headerRowDxfId="11" dataDxfId="10" totalsRowDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{30CD9512-EB44-4CF4-9A36-02A1E4DC7CB1}" name="TabelSkenarioBlackBox4" displayName="TabelSkenarioBlackBox4" ref="A1:H145" headerRowDxfId="21" dataDxfId="20" totalsRowDxfId="19">
   <tableColumns count="8">
-    <tableColumn id="3" xr3:uid="{3800B9E6-4A5C-41EF-8CB5-73EA38DC26AD}" name="ID Skenario" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{C90EEBC5-FAD5-4009-85F6-38014CB0F104}" name="Kebutuhan Fungsional" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{4174CD64-F2A7-4D05-949B-CE14FC4CCE52}" name="Skenario Pengujian" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{1025CE13-E3E1-43F1-9CDF-7577BE1821F9}" name="Prasyarat" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{FD667C8E-A5B9-407F-A579-CF9B2B3C8E40}" name="Data Uji" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{A6229C36-A9C9-4F70-BCE6-31E277610D9F}" name="Langkah Pengujian" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{6F37B44A-5DEF-44ED-B1B6-95D38DB78B84}" name="Ekspektasi Hasil" dataDxfId="2"/>
-    <tableColumn id="1" xr3:uid="{BE777815-17A2-49C5-A31D-52DD12249D48}" name="Hasil" dataDxfId="0" totalsRowDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{3800B9E6-4A5C-41EF-8CB5-73EA38DC26AD}" name="ID Skenario" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{C90EEBC5-FAD5-4009-85F6-38014CB0F104}" name="Kebutuhan Fungsional" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{4174CD64-F2A7-4D05-949B-CE14FC4CCE52}" name="Skenario Pengujian" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{1025CE13-E3E1-43F1-9CDF-7577BE1821F9}" name="Prasyarat" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{FD667C8E-A5B9-407F-A579-CF9B2B3C8E40}" name="Data Uji" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{A6229C36-A9C9-4F70-BCE6-31E277610D9F}" name="Langkah Pengujian" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{6F37B44A-5DEF-44ED-B1B6-95D38DB78B84}" name="Ekspektasi Hasil" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{BE777815-17A2-49C5-A31D-52DD12249D48}" name="Hasil" dataDxfId="11" totalsRowDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7543,394 +7543,394 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:2" ht="15" thickBot="1">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>960</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="21" t="s">
         <v>961</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="120.75" thickBot="1">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="23" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="165.75" thickBot="1">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="23" t="s">
         <v>962</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="135.75" thickBot="1">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="23" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="180.75" thickBot="1">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="23" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="105.75" thickBot="1">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="23" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="105.75" thickBot="1">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="23" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="120.75" thickBot="1">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="23" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="105.75" thickBot="1">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="23" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="135.75" thickBot="1">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="23" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="135.75" thickBot="1">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="23" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="120.75" thickBot="1">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="22" t="s">
         <v>207</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="23" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="135.75" thickBot="1">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="23" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="120.75" thickBot="1">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="22" t="s">
         <v>246</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="23" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="105.75" thickBot="1">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="22" t="s">
         <v>266</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="23" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="120.75" thickBot="1">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="23" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="150.75" thickBot="1">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="22" t="s">
         <v>305</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="23" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="165.75" thickBot="1">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="22" t="s">
         <v>324</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="23" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="150.75" thickBot="1">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="22" t="s">
         <v>344</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="23" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="135.75" thickBot="1">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="22" t="s">
         <v>364</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="23" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="135.75" thickBot="1">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="22" t="s">
         <v>383</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="23" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="105.75" thickBot="1">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="22" t="s">
         <v>403</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="23" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="255.75" thickBot="1">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="22" t="s">
         <v>423</v>
       </c>
-      <c r="B23" s="24" t="s">
+      <c r="B23" s="23" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="225.75" thickBot="1">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="22" t="s">
         <v>443</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="23" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="135.75" thickBot="1">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="22" t="s">
         <v>462</v>
       </c>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="23" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="120.75" thickBot="1">
-      <c r="A26" s="23" t="s">
+      <c r="A26" s="22" t="s">
         <v>481</v>
       </c>
-      <c r="B26" s="24" t="s">
+      <c r="B26" s="23" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="105.75" thickBot="1">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="22" t="s">
         <v>499</v>
       </c>
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="23" t="s">
         <v>500</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="150.75" thickBot="1">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="22" t="s">
         <v>519</v>
       </c>
-      <c r="B28" s="24" t="s">
+      <c r="B28" s="23" t="s">
         <v>520</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="150.75" thickBot="1">
-      <c r="A29" s="23" t="s">
+      <c r="A29" s="22" t="s">
         <v>539</v>
       </c>
-      <c r="B29" s="24" t="s">
+      <c r="B29" s="23" t="s">
         <v>540</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="120.75" thickBot="1">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="22" t="s">
         <v>556</v>
       </c>
-      <c r="B30" s="24" t="s">
+      <c r="B30" s="23" t="s">
         <v>557</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="165.75" thickBot="1">
-      <c r="A31" s="23" t="s">
+      <c r="A31" s="22" t="s">
         <v>576</v>
       </c>
-      <c r="B31" s="24" t="s">
+      <c r="B31" s="23" t="s">
         <v>577</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="150.75" thickBot="1">
-      <c r="A32" s="23" t="s">
+      <c r="A32" s="22" t="s">
         <v>596</v>
       </c>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="23" t="s">
         <v>597</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="165.75" thickBot="1">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="22" t="s">
         <v>616</v>
       </c>
-      <c r="B33" s="24" t="s">
+      <c r="B33" s="23" t="s">
         <v>617</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="180.75" thickBot="1">
-      <c r="A34" s="23" t="s">
+      <c r="A34" s="22" t="s">
         <v>634</v>
       </c>
-      <c r="B34" s="24" t="s">
+      <c r="B34" s="23" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="150.75" thickBot="1">
-      <c r="A35" s="23" t="s">
+      <c r="A35" s="22" t="s">
         <v>654</v>
       </c>
-      <c r="B35" s="24" t="s">
+      <c r="B35" s="23" t="s">
         <v>655</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="135.75" thickBot="1">
-      <c r="A36" s="23" t="s">
+      <c r="A36" s="22" t="s">
         <v>674</v>
       </c>
-      <c r="B36" s="24" t="s">
+      <c r="B36" s="23" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="135.75" thickBot="1">
-      <c r="A37" s="23" t="s">
+      <c r="A37" s="22" t="s">
         <v>693</v>
       </c>
-      <c r="B37" s="24" t="s">
+      <c r="B37" s="23" t="s">
         <v>694</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="135.75" thickBot="1">
-      <c r="A38" s="23" t="s">
+      <c r="A38" s="22" t="s">
         <v>713</v>
       </c>
-      <c r="B38" s="24" t="s">
+      <c r="B38" s="23" t="s">
         <v>714</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="120.75" thickBot="1">
-      <c r="A39" s="23" t="s">
+      <c r="A39" s="22" t="s">
         <v>731</v>
       </c>
-      <c r="B39" s="24" t="s">
+      <c r="B39" s="23" t="s">
         <v>732</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="165.75" thickBot="1">
-      <c r="A40" s="23" t="s">
+      <c r="A40" s="22" t="s">
         <v>751</v>
       </c>
-      <c r="B40" s="24" t="s">
+      <c r="B40" s="23" t="s">
         <v>752</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="195.75" thickBot="1">
-      <c r="A41" s="23" t="s">
+      <c r="A41" s="22" t="s">
         <v>771</v>
       </c>
-      <c r="B41" s="24" t="s">
+      <c r="B41" s="23" t="s">
         <v>772</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="180.75" thickBot="1">
-      <c r="A42" s="23" t="s">
+      <c r="A42" s="22" t="s">
         <v>790</v>
       </c>
-      <c r="B42" s="24" t="s">
+      <c r="B42" s="23" t="s">
         <v>791</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="120.75" thickBot="1">
-      <c r="A43" s="23" t="s">
+      <c r="A43" s="22" t="s">
         <v>810</v>
       </c>
-      <c r="B43" s="24" t="s">
+      <c r="B43" s="23" t="s">
         <v>811</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="150">
-      <c r="A44" s="25" t="s">
+      <c r="A44" s="24" t="s">
         <v>830</v>
       </c>
-      <c r="B44" s="26" t="s">
+      <c r="B44" s="25" t="s">
         <v>831</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="225.75" thickBot="1">
-      <c r="A45" s="23" t="s">
+      <c r="A45" s="22" t="s">
         <v>850</v>
       </c>
-      <c r="B45" s="24" t="s">
+      <c r="B45" s="23" t="s">
         <v>851</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="135.75" thickBot="1">
-      <c r="A46" s="23" t="s">
+      <c r="A46" s="22" t="s">
         <v>870</v>
       </c>
-      <c r="B46" s="24" t="s">
+      <c r="B46" s="23" t="s">
         <v>871</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="255.75" thickBot="1">
-      <c r="A47" s="23" t="s">
+      <c r="A47" s="22" t="s">
         <v>889</v>
       </c>
-      <c r="B47" s="24" t="s">
+      <c r="B47" s="23" t="s">
         <v>890</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="120.75" thickBot="1">
-      <c r="A48" s="23" t="s">
+      <c r="A48" s="22" t="s">
         <v>909</v>
       </c>
-      <c r="B48" s="24" t="s">
+      <c r="B48" s="23" t="s">
         <v>910</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="165.75" thickBot="1">
-      <c r="A49" s="23" t="s">
+      <c r="A49" s="22" t="s">
         <v>929</v>
       </c>
-      <c r="B49" s="24" t="s">
+      <c r="B49" s="23" t="s">
         <v>930</v>
       </c>
     </row>
@@ -7952,7 +7952,7 @@
     <col min="5" max="5" width="37" style="18" customWidth="1"/>
     <col min="6" max="6" width="31.625" style="18" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="45.125" style="18" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="24.875" style="30" customWidth="1"/>
+    <col min="8" max="8" width="24.875" style="29" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26.25" customHeight="1">
@@ -8003,7 +8003,7 @@
       <c r="G2" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="27" t="s">
+      <c r="H2" s="26" t="s">
         <v>963</v>
       </c>
     </row>
@@ -8029,7 +8029,7 @@
       <c r="G3" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="27" t="s">
+      <c r="H3" s="26" t="s">
         <v>963</v>
       </c>
     </row>
@@ -8055,7 +8055,7 @@
       <c r="G4" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="27" t="s">
+      <c r="H4" s="26" t="s">
         <v>963</v>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
       <c r="G5" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="27" t="s">
         <v>963</v>
       </c>
     </row>
@@ -8107,7 +8107,7 @@
       <c r="G6" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="28"/>
+      <c r="H6" s="27"/>
     </row>
     <row r="7" spans="1:8" ht="66" customHeight="1">
       <c r="A7" s="16" t="s">
@@ -8131,7 +8131,7 @@
       <c r="G7" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="28"/>
+      <c r="H7" s="27"/>
     </row>
     <row r="8" spans="1:8" ht="66" customHeight="1">
       <c r="A8" s="16" t="s">
@@ -8155,7 +8155,7 @@
       <c r="G8" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="28"/>
+      <c r="H8" s="27"/>
     </row>
     <row r="9" spans="1:8" ht="66" customHeight="1">
       <c r="A9" s="16" t="s">
@@ -8179,7 +8179,7 @@
       <c r="G9" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="H9" s="28"/>
+      <c r="H9" s="27"/>
     </row>
     <row r="10" spans="1:8" ht="66" customHeight="1">
       <c r="A10" s="16" t="s">
@@ -8203,7 +8203,7 @@
       <c r="G10" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="H10" s="28"/>
+      <c r="H10" s="27"/>
     </row>
     <row r="11" spans="1:8" ht="66" customHeight="1">
       <c r="A11" s="16" t="s">
@@ -8227,7 +8227,7 @@
       <c r="G11" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="H11" s="28"/>
+      <c r="H11" s="27"/>
     </row>
     <row r="12" spans="1:8" ht="66" customHeight="1">
       <c r="A12" s="16" t="s">
@@ -8251,7 +8251,7 @@
       <c r="G12" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="H12" s="28"/>
+      <c r="H12" s="27"/>
     </row>
     <row r="13" spans="1:8" ht="66" customHeight="1">
       <c r="A13" s="16" t="s">
@@ -8275,7 +8275,7 @@
       <c r="G13" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="28"/>
+      <c r="H13" s="27"/>
     </row>
     <row r="14" spans="1:8" ht="66" customHeight="1">
       <c r="A14" s="16" t="s">
@@ -8299,7 +8299,7 @@
       <c r="G14" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="H14" s="28"/>
+      <c r="H14" s="27"/>
     </row>
     <row r="15" spans="1:8" ht="66" customHeight="1">
       <c r="A15" s="16" t="s">
@@ -8323,7 +8323,7 @@
       <c r="G15" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="28"/>
+      <c r="H15" s="27"/>
     </row>
     <row r="16" spans="1:8" ht="66" customHeight="1">
       <c r="A16" s="16" t="s">
@@ -8347,7 +8347,7 @@
       <c r="G16" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="H16" s="28"/>
+      <c r="H16" s="27"/>
     </row>
     <row r="17" spans="1:8" ht="66" customHeight="1">
       <c r="A17" s="16" t="s">
@@ -8371,7 +8371,7 @@
       <c r="G17" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="H17" s="28"/>
+      <c r="H17" s="27"/>
     </row>
     <row r="18" spans="1:8" ht="66" customHeight="1">
       <c r="A18" s="16" t="s">
@@ -8395,7 +8395,7 @@
       <c r="G18" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="H18" s="28"/>
+      <c r="H18" s="27"/>
     </row>
     <row r="19" spans="1:8" ht="66" customHeight="1">
       <c r="A19" s="16" t="s">
@@ -8419,7 +8419,7 @@
       <c r="G19" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H19" s="28"/>
+      <c r="H19" s="27"/>
     </row>
     <row r="20" spans="1:8" ht="66" customHeight="1">
       <c r="A20" s="16" t="s">
@@ -8443,7 +8443,7 @@
       <c r="G20" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="H20" s="28"/>
+      <c r="H20" s="27"/>
     </row>
     <row r="21" spans="1:8" ht="66" customHeight="1">
       <c r="A21" s="16" t="s">
@@ -8467,7 +8467,7 @@
       <c r="G21" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H21" s="28"/>
+      <c r="H21" s="27"/>
     </row>
     <row r="22" spans="1:8" ht="66" customHeight="1">
       <c r="A22" s="16" t="s">
@@ -8491,7 +8491,7 @@
       <c r="G22" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="H22" s="28"/>
+      <c r="H22" s="27"/>
     </row>
     <row r="23" spans="1:8" ht="66" customHeight="1">
       <c r="A23" s="16" t="s">
@@ -8515,7 +8515,7 @@
       <c r="G23" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="H23" s="28"/>
+      <c r="H23" s="27"/>
     </row>
     <row r="24" spans="1:8" ht="66" customHeight="1">
       <c r="A24" s="16" t="s">
@@ -8539,7 +8539,7 @@
       <c r="G24" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="H24" s="28"/>
+      <c r="H24" s="27"/>
     </row>
     <row r="25" spans="1:8" ht="66" customHeight="1">
       <c r="A25" s="16" t="s">
@@ -8563,7 +8563,7 @@
       <c r="G25" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="H25" s="28"/>
+      <c r="H25" s="27"/>
     </row>
     <row r="26" spans="1:8" ht="66" customHeight="1">
       <c r="A26" s="16" t="s">
@@ -8587,7 +8587,7 @@
       <c r="G26" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="H26" s="28"/>
+      <c r="H26" s="27"/>
     </row>
     <row r="27" spans="1:8" ht="66" customHeight="1">
       <c r="A27" s="16" t="s">
@@ -8611,7 +8611,7 @@
       <c r="G27" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="H27" s="28"/>
+      <c r="H27" s="27"/>
     </row>
     <row r="28" spans="1:8" ht="66" customHeight="1">
       <c r="A28" s="16" t="s">
@@ -8635,7 +8635,7 @@
       <c r="G28" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="H28" s="28"/>
+      <c r="H28" s="27"/>
     </row>
     <row r="29" spans="1:8" ht="66" customHeight="1">
       <c r="A29" s="16" t="s">
@@ -8659,7 +8659,7 @@
       <c r="G29" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="H29" s="28"/>
+      <c r="H29" s="27"/>
     </row>
     <row r="30" spans="1:8" ht="66" customHeight="1">
       <c r="A30" s="16" t="s">
@@ -8683,7 +8683,7 @@
       <c r="G30" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="H30" s="28"/>
+      <c r="H30" s="27"/>
     </row>
     <row r="31" spans="1:8" ht="66" customHeight="1">
       <c r="A31" s="16" t="s">
@@ -8707,7 +8707,7 @@
       <c r="G31" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="H31" s="28"/>
+      <c r="H31" s="27"/>
     </row>
     <row r="32" spans="1:8" ht="66" customHeight="1">
       <c r="A32" s="16" t="s">
@@ -8731,7 +8731,7 @@
       <c r="G32" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="H32" s="28"/>
+      <c r="H32" s="27"/>
     </row>
     <row r="33" spans="1:8" ht="66" customHeight="1">
       <c r="A33" s="16" t="s">
@@ -8755,7 +8755,7 @@
       <c r="G33" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="H33" s="28"/>
+      <c r="H33" s="27"/>
     </row>
     <row r="34" spans="1:8" ht="66" customHeight="1">
       <c r="A34" s="16" t="s">
@@ -8779,7 +8779,7 @@
       <c r="G34" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="H34" s="28"/>
+      <c r="H34" s="27"/>
     </row>
     <row r="35" spans="1:8" ht="66" customHeight="1">
       <c r="A35" s="16" t="s">
@@ -8803,7 +8803,7 @@
       <c r="G35" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="H35" s="28"/>
+      <c r="H35" s="27"/>
     </row>
     <row r="36" spans="1:8" ht="66" customHeight="1">
       <c r="A36" s="16" t="s">
@@ -8827,7 +8827,7 @@
       <c r="G36" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="H36" s="28"/>
+      <c r="H36" s="27"/>
     </row>
     <row r="37" spans="1:8" ht="66" customHeight="1">
       <c r="A37" s="16" t="s">
@@ -8851,7 +8851,7 @@
       <c r="G37" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="H37" s="28"/>
+      <c r="H37" s="27"/>
     </row>
     <row r="38" spans="1:8" ht="66" customHeight="1">
       <c r="A38" s="16" t="s">
@@ -8875,7 +8875,7 @@
       <c r="G38" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="H38" s="28"/>
+      <c r="H38" s="27"/>
     </row>
     <row r="39" spans="1:8" ht="66" customHeight="1">
       <c r="A39" s="16" t="s">
@@ -8899,7 +8899,7 @@
       <c r="G39" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="H39" s="28"/>
+      <c r="H39" s="27"/>
     </row>
     <row r="40" spans="1:8" ht="66" customHeight="1">
       <c r="A40" s="16" t="s">
@@ -8923,7 +8923,7 @@
       <c r="G40" s="17" t="s">
         <v>265</v>
       </c>
-      <c r="H40" s="28"/>
+      <c r="H40" s="27"/>
     </row>
     <row r="41" spans="1:8" ht="66" customHeight="1">
       <c r="A41" s="16" t="s">
@@ -8947,7 +8947,7 @@
       <c r="G41" s="17" t="s">
         <v>273</v>
       </c>
-      <c r="H41" s="28"/>
+      <c r="H41" s="27"/>
     </row>
     <row r="42" spans="1:8" ht="66" customHeight="1">
       <c r="A42" s="16" t="s">
@@ -8971,7 +8971,7 @@
       <c r="G42" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="H42" s="28"/>
+      <c r="H42" s="27"/>
     </row>
     <row r="43" spans="1:8" ht="66" customHeight="1">
       <c r="A43" s="16" t="s">
@@ -8995,7 +8995,7 @@
       <c r="G43" s="17" t="s">
         <v>284</v>
       </c>
-      <c r="H43" s="28"/>
+      <c r="H43" s="27"/>
     </row>
     <row r="44" spans="1:8" ht="66" customHeight="1">
       <c r="A44" s="16" t="s">
@@ -9019,7 +9019,7 @@
       <c r="G44" s="17" t="s">
         <v>292</v>
       </c>
-      <c r="H44" s="28"/>
+      <c r="H44" s="27"/>
     </row>
     <row r="45" spans="1:8" ht="66" customHeight="1">
       <c r="A45" s="16" t="s">
@@ -9043,7 +9043,7 @@
       <c r="G45" s="17" t="s">
         <v>298</v>
       </c>
-      <c r="H45" s="28"/>
+      <c r="H45" s="27"/>
     </row>
     <row r="46" spans="1:8" ht="66" customHeight="1">
       <c r="A46" s="16" t="s">
@@ -9067,7 +9067,7 @@
       <c r="G46" s="17" t="s">
         <v>304</v>
       </c>
-      <c r="H46" s="28"/>
+      <c r="H46" s="27"/>
     </row>
     <row r="47" spans="1:8" ht="66" customHeight="1">
       <c r="A47" s="16" t="s">
@@ -9091,7 +9091,7 @@
       <c r="G47" s="17" t="s">
         <v>312</v>
       </c>
-      <c r="H47" s="28"/>
+      <c r="H47" s="27"/>
     </row>
     <row r="48" spans="1:8" ht="66" customHeight="1">
       <c r="A48" s="16" t="s">
@@ -9115,7 +9115,7 @@
       <c r="G48" s="17" t="s">
         <v>318</v>
       </c>
-      <c r="H48" s="28"/>
+      <c r="H48" s="27"/>
     </row>
     <row r="49" spans="1:8" ht="66" customHeight="1">
       <c r="A49" s="16" t="s">
@@ -9139,7 +9139,7 @@
       <c r="G49" s="17" t="s">
         <v>323</v>
       </c>
-      <c r="H49" s="28"/>
+      <c r="H49" s="27"/>
     </row>
     <row r="50" spans="1:8" ht="66" customHeight="1">
       <c r="A50" s="16" t="s">
@@ -9163,7 +9163,7 @@
       <c r="G50" s="17" t="s">
         <v>331</v>
       </c>
-      <c r="H50" s="28"/>
+      <c r="H50" s="27"/>
     </row>
     <row r="51" spans="1:8" ht="66" customHeight="1">
       <c r="A51" s="16" t="s">
@@ -9187,7 +9187,7 @@
       <c r="G51" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="H51" s="28"/>
+      <c r="H51" s="27"/>
     </row>
     <row r="52" spans="1:8" ht="66" customHeight="1">
       <c r="A52" s="16" t="s">
@@ -9211,7 +9211,7 @@
       <c r="G52" s="17" t="s">
         <v>343</v>
       </c>
-      <c r="H52" s="28"/>
+      <c r="H52" s="27"/>
     </row>
     <row r="53" spans="1:8" ht="66" customHeight="1">
       <c r="A53" s="16" t="s">
@@ -9235,7 +9235,7 @@
       <c r="G53" s="17" t="s">
         <v>351</v>
       </c>
-      <c r="H53" s="28"/>
+      <c r="H53" s="27"/>
     </row>
     <row r="54" spans="1:8" ht="66" customHeight="1">
       <c r="A54" s="16" t="s">
@@ -9259,7 +9259,7 @@
       <c r="G54" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="H54" s="28"/>
+      <c r="H54" s="27"/>
     </row>
     <row r="55" spans="1:8" ht="66" customHeight="1">
       <c r="A55" s="16" t="s">
@@ -9283,7 +9283,7 @@
       <c r="G55" s="17" t="s">
         <v>363</v>
       </c>
-      <c r="H55" s="28"/>
+      <c r="H55" s="27"/>
     </row>
     <row r="56" spans="1:8" ht="66" customHeight="1">
       <c r="A56" s="16" t="s">
@@ -9307,7 +9307,7 @@
       <c r="G56" s="17" t="s">
         <v>371</v>
       </c>
-      <c r="H56" s="28"/>
+      <c r="H56" s="27"/>
     </row>
     <row r="57" spans="1:8" ht="66" customHeight="1">
       <c r="A57" s="16" t="s">
@@ -9331,7 +9331,7 @@
       <c r="G57" s="17" t="s">
         <v>376</v>
       </c>
-      <c r="H57" s="28"/>
+      <c r="H57" s="27"/>
     </row>
     <row r="58" spans="1:8" ht="66" customHeight="1">
       <c r="A58" s="16" t="s">
@@ -9355,7 +9355,7 @@
       <c r="G58" s="17" t="s">
         <v>382</v>
       </c>
-      <c r="H58" s="28"/>
+      <c r="H58" s="27"/>
     </row>
     <row r="59" spans="1:8" ht="66" customHeight="1">
       <c r="A59" s="16" t="s">
@@ -9379,7 +9379,7 @@
       <c r="G59" s="17" t="s">
         <v>390</v>
       </c>
-      <c r="H59" s="28"/>
+      <c r="H59" s="27"/>
     </row>
     <row r="60" spans="1:8" ht="66" customHeight="1">
       <c r="A60" s="16" t="s">
@@ -9403,7 +9403,7 @@
       <c r="G60" s="17" t="s">
         <v>396</v>
       </c>
-      <c r="H60" s="28"/>
+      <c r="H60" s="27"/>
     </row>
     <row r="61" spans="1:8" ht="66" customHeight="1">
       <c r="A61" s="16" t="s">
@@ -9427,7 +9427,7 @@
       <c r="G61" s="17" t="s">
         <v>402</v>
       </c>
-      <c r="H61" s="28"/>
+      <c r="H61" s="27"/>
     </row>
     <row r="62" spans="1:8" ht="66" customHeight="1">
       <c r="A62" s="16" t="s">
@@ -9451,7 +9451,7 @@
       <c r="G62" s="17" t="s">
         <v>410</v>
       </c>
-      <c r="H62" s="28"/>
+      <c r="H62" s="27"/>
     </row>
     <row r="63" spans="1:8" ht="66" customHeight="1">
       <c r="A63" s="16" t="s">
@@ -9475,7 +9475,7 @@
       <c r="G63" s="17" t="s">
         <v>416</v>
       </c>
-      <c r="H63" s="28"/>
+      <c r="H63" s="27"/>
     </row>
     <row r="64" spans="1:8" ht="66" customHeight="1">
       <c r="A64" s="16" t="s">
@@ -9499,7 +9499,7 @@
       <c r="G64" s="17" t="s">
         <v>422</v>
       </c>
-      <c r="H64" s="28"/>
+      <c r="H64" s="27"/>
     </row>
     <row r="65" spans="1:8" ht="66" customHeight="1">
       <c r="A65" s="16" t="s">
@@ -9523,7 +9523,7 @@
       <c r="G65" s="17" t="s">
         <v>430</v>
       </c>
-      <c r="H65" s="28"/>
+      <c r="H65" s="27"/>
     </row>
     <row r="66" spans="1:8" ht="66" customHeight="1">
       <c r="A66" s="16" t="s">
@@ -9547,7 +9547,7 @@
       <c r="G66" s="17" t="s">
         <v>436</v>
       </c>
-      <c r="H66" s="28"/>
+      <c r="H66" s="27"/>
     </row>
     <row r="67" spans="1:8" ht="66" customHeight="1">
       <c r="A67" s="16" t="s">
@@ -9571,7 +9571,7 @@
       <c r="G67" s="17" t="s">
         <v>442</v>
       </c>
-      <c r="H67" s="28"/>
+      <c r="H67" s="27"/>
     </row>
     <row r="68" spans="1:8" ht="66" customHeight="1">
       <c r="A68" s="16" t="s">
@@ -9595,7 +9595,7 @@
       <c r="G68" s="17" t="s">
         <v>450</v>
       </c>
-      <c r="H68" s="28"/>
+      <c r="H68" s="27"/>
     </row>
     <row r="69" spans="1:8" ht="66" customHeight="1">
       <c r="A69" s="16" t="s">
@@ -9619,7 +9619,7 @@
       <c r="G69" s="17" t="s">
         <v>455</v>
       </c>
-      <c r="H69" s="28"/>
+      <c r="H69" s="27"/>
     </row>
     <row r="70" spans="1:8" ht="66" customHeight="1">
       <c r="A70" s="16" t="s">
@@ -9643,7 +9643,7 @@
       <c r="G70" s="17" t="s">
         <v>461</v>
       </c>
-      <c r="H70" s="28"/>
+      <c r="H70" s="27"/>
     </row>
     <row r="71" spans="1:8" ht="66" customHeight="1">
       <c r="A71" s="16" t="s">
@@ -9667,7 +9667,7 @@
       <c r="G71" s="17" t="s">
         <v>469</v>
       </c>
-      <c r="H71" s="28"/>
+      <c r="H71" s="27"/>
     </row>
     <row r="72" spans="1:8" ht="66" customHeight="1">
       <c r="A72" s="16" t="s">
@@ -9691,7 +9691,7 @@
       <c r="G72" s="17" t="s">
         <v>475</v>
       </c>
-      <c r="H72" s="28"/>
+      <c r="H72" s="27"/>
     </row>
     <row r="73" spans="1:8" ht="66" customHeight="1">
       <c r="A73" s="16" t="s">
@@ -9715,7 +9715,7 @@
       <c r="G73" s="17" t="s">
         <v>480</v>
       </c>
-      <c r="H73" s="28"/>
+      <c r="H73" s="27"/>
     </row>
     <row r="74" spans="1:8" ht="66" customHeight="1">
       <c r="A74" s="16" t="s">
@@ -9739,7 +9739,7 @@
       <c r="G74" s="17" t="s">
         <v>487</v>
       </c>
-      <c r="H74" s="28"/>
+      <c r="H74" s="27"/>
     </row>
     <row r="75" spans="1:8" ht="66" customHeight="1">
       <c r="A75" s="16" t="s">
@@ -9763,7 +9763,7 @@
       <c r="G75" s="17" t="s">
         <v>493</v>
       </c>
-      <c r="H75" s="28"/>
+      <c r="H75" s="27"/>
     </row>
     <row r="76" spans="1:8" ht="66" customHeight="1">
       <c r="A76" s="16" t="s">
@@ -9787,7 +9787,7 @@
       <c r="G76" s="17" t="s">
         <v>498</v>
       </c>
-      <c r="H76" s="28"/>
+      <c r="H76" s="27"/>
     </row>
     <row r="77" spans="1:8" ht="66" customHeight="1">
       <c r="A77" s="16" t="s">
@@ -9811,7 +9811,7 @@
       <c r="G77" s="17" t="s">
         <v>506</v>
       </c>
-      <c r="H77" s="28"/>
+      <c r="H77" s="27"/>
     </row>
     <row r="78" spans="1:8" ht="66" customHeight="1">
       <c r="A78" s="16" t="s">
@@ -9835,7 +9835,7 @@
       <c r="G78" s="17" t="s">
         <v>512</v>
       </c>
-      <c r="H78" s="28"/>
+      <c r="H78" s="27"/>
     </row>
     <row r="79" spans="1:8" ht="66" customHeight="1">
       <c r="A79" s="16" t="s">
@@ -9859,7 +9859,7 @@
       <c r="G79" s="17" t="s">
         <v>518</v>
       </c>
-      <c r="H79" s="28"/>
+      <c r="H79" s="27"/>
     </row>
     <row r="80" spans="1:8" ht="66" customHeight="1">
       <c r="A80" s="16" t="s">
@@ -9883,7 +9883,7 @@
       <c r="G80" s="17" t="s">
         <v>526</v>
       </c>
-      <c r="H80" s="28"/>
+      <c r="H80" s="27"/>
     </row>
     <row r="81" spans="1:8" ht="66" customHeight="1">
       <c r="A81" s="16" t="s">
@@ -9907,7 +9907,7 @@
       <c r="G81" s="17" t="s">
         <v>532</v>
       </c>
-      <c r="H81" s="28"/>
+      <c r="H81" s="27"/>
     </row>
     <row r="82" spans="1:8" ht="66" customHeight="1">
       <c r="A82" s="16" t="s">
@@ -9931,7 +9931,7 @@
       <c r="G82" s="17" t="s">
         <v>538</v>
       </c>
-      <c r="H82" s="28"/>
+      <c r="H82" s="27"/>
     </row>
     <row r="83" spans="1:8" ht="66" customHeight="1">
       <c r="A83" s="16" t="s">
@@ -9955,7 +9955,7 @@
       <c r="G83" s="17" t="s">
         <v>544</v>
       </c>
-      <c r="H83" s="28"/>
+      <c r="H83" s="27"/>
     </row>
     <row r="84" spans="1:8" ht="66" customHeight="1">
       <c r="A84" s="16" t="s">
@@ -9979,7 +9979,7 @@
       <c r="G84" s="17" t="s">
         <v>550</v>
       </c>
-      <c r="H84" s="28"/>
+      <c r="H84" s="27"/>
     </row>
     <row r="85" spans="1:8" ht="66" customHeight="1">
       <c r="A85" s="16" t="s">
@@ -10003,7 +10003,7 @@
       <c r="G85" s="17" t="s">
         <v>422</v>
       </c>
-      <c r="H85" s="28"/>
+      <c r="H85" s="27"/>
     </row>
     <row r="86" spans="1:8" ht="66" customHeight="1">
       <c r="A86" s="16" t="s">
@@ -10027,7 +10027,7 @@
       <c r="G86" s="17" t="s">
         <v>563</v>
       </c>
-      <c r="H86" s="28"/>
+      <c r="H86" s="27"/>
     </row>
     <row r="87" spans="1:8" ht="66" customHeight="1">
       <c r="A87" s="16" t="s">
@@ -10051,7 +10051,7 @@
       <c r="G87" s="17" t="s">
         <v>569</v>
       </c>
-      <c r="H87" s="28"/>
+      <c r="H87" s="27"/>
     </row>
     <row r="88" spans="1:8" ht="66" customHeight="1">
       <c r="A88" s="16" t="s">
@@ -10075,7 +10075,7 @@
       <c r="G88" s="17" t="s">
         <v>575</v>
       </c>
-      <c r="H88" s="28"/>
+      <c r="H88" s="27"/>
     </row>
     <row r="89" spans="1:8" ht="66" customHeight="1">
       <c r="A89" s="16" t="s">
@@ -10099,7 +10099,7 @@
       <c r="G89" s="17" t="s">
         <v>583</v>
       </c>
-      <c r="H89" s="28"/>
+      <c r="H89" s="27"/>
     </row>
     <row r="90" spans="1:8" ht="66" customHeight="1">
       <c r="A90" s="16" t="s">
@@ -10123,7 +10123,7 @@
       <c r="G90" s="17" t="s">
         <v>589</v>
       </c>
-      <c r="H90" s="28"/>
+      <c r="H90" s="27"/>
     </row>
     <row r="91" spans="1:8" ht="66" customHeight="1">
       <c r="A91" s="16" t="s">
@@ -10147,7 +10147,7 @@
       <c r="G91" s="17" t="s">
         <v>595</v>
       </c>
-      <c r="H91" s="28"/>
+      <c r="H91" s="27"/>
     </row>
     <row r="92" spans="1:8" ht="66" customHeight="1">
       <c r="A92" s="16" t="s">
@@ -10171,7 +10171,7 @@
       <c r="G92" s="17" t="s">
         <v>603</v>
       </c>
-      <c r="H92" s="28"/>
+      <c r="H92" s="27"/>
     </row>
     <row r="93" spans="1:8" ht="66" customHeight="1">
       <c r="A93" s="16" t="s">
@@ -10195,7 +10195,7 @@
       <c r="G93" s="17" t="s">
         <v>609</v>
       </c>
-      <c r="H93" s="28"/>
+      <c r="H93" s="27"/>
     </row>
     <row r="94" spans="1:8" ht="66" customHeight="1">
       <c r="A94" s="16" t="s">
@@ -10219,7 +10219,7 @@
       <c r="G94" s="17" t="s">
         <v>615</v>
       </c>
-      <c r="H94" s="28"/>
+      <c r="H94" s="27"/>
     </row>
     <row r="95" spans="1:8" ht="66" customHeight="1">
       <c r="A95" s="16" t="s">
@@ -10243,7 +10243,7 @@
       <c r="G95" s="17" t="s">
         <v>623</v>
       </c>
-      <c r="H95" s="28"/>
+      <c r="H95" s="27"/>
     </row>
     <row r="96" spans="1:8" ht="66" customHeight="1">
       <c r="A96" s="16" t="s">
@@ -10267,7 +10267,7 @@
       <c r="G96" s="17" t="s">
         <v>629</v>
       </c>
-      <c r="H96" s="28"/>
+      <c r="H96" s="27"/>
     </row>
     <row r="97" spans="1:8" ht="66" customHeight="1">
       <c r="A97" s="16" t="s">
@@ -10291,7 +10291,7 @@
       <c r="G97" s="17" t="s">
         <v>633</v>
       </c>
-      <c r="H97" s="28"/>
+      <c r="H97" s="27"/>
     </row>
     <row r="98" spans="1:8" ht="66" customHeight="1">
       <c r="A98" s="16" t="s">
@@ -10315,7 +10315,7 @@
       <c r="G98" s="17" t="s">
         <v>641</v>
       </c>
-      <c r="H98" s="28"/>
+      <c r="H98" s="27"/>
     </row>
     <row r="99" spans="1:8" ht="66" customHeight="1">
       <c r="A99" s="16" t="s">
@@ -10339,7 +10339,7 @@
       <c r="G99" s="17" t="s">
         <v>647</v>
       </c>
-      <c r="H99" s="28"/>
+      <c r="H99" s="27"/>
     </row>
     <row r="100" spans="1:8" ht="66" customHeight="1">
       <c r="A100" s="16" t="s">
@@ -10363,7 +10363,7 @@
       <c r="G100" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="H100" s="28"/>
+      <c r="H100" s="27"/>
     </row>
     <row r="101" spans="1:8" ht="66" customHeight="1">
       <c r="A101" s="16" t="s">
@@ -10387,7 +10387,7 @@
       <c r="G101" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="H101" s="28"/>
+      <c r="H101" s="27"/>
     </row>
     <row r="102" spans="1:8" ht="66" customHeight="1">
       <c r="A102" s="16" t="s">
@@ -10411,7 +10411,7 @@
       <c r="G102" s="17" t="s">
         <v>667</v>
       </c>
-      <c r="H102" s="28"/>
+      <c r="H102" s="27"/>
     </row>
     <row r="103" spans="1:8" ht="66" customHeight="1">
       <c r="A103" s="16" t="s">
@@ -10435,7 +10435,7 @@
       <c r="G103" s="17" t="s">
         <v>673</v>
       </c>
-      <c r="H103" s="28"/>
+      <c r="H103" s="27"/>
     </row>
     <row r="104" spans="1:8" ht="66" customHeight="1">
       <c r="A104" s="16" t="s">
@@ -10459,7 +10459,7 @@
       <c r="G104" s="17" t="s">
         <v>681</v>
       </c>
-      <c r="H104" s="28"/>
+      <c r="H104" s="27"/>
     </row>
     <row r="105" spans="1:8" ht="66" customHeight="1">
       <c r="A105" s="16" t="s">
@@ -10483,7 +10483,7 @@
       <c r="G105" s="17" t="s">
         <v>687</v>
       </c>
-      <c r="H105" s="28"/>
+      <c r="H105" s="27"/>
     </row>
     <row r="106" spans="1:8" ht="66" customHeight="1">
       <c r="A106" s="16" t="s">
@@ -10507,7 +10507,7 @@
       <c r="G106" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="H106" s="28"/>
+      <c r="H106" s="27"/>
     </row>
     <row r="107" spans="1:8" ht="66" customHeight="1">
       <c r="A107" s="16" t="s">
@@ -10531,7 +10531,7 @@
       <c r="G107" s="17" t="s">
         <v>700</v>
       </c>
-      <c r="H107" s="28"/>
+      <c r="H107" s="27"/>
     </row>
     <row r="108" spans="1:8" ht="66" customHeight="1">
       <c r="A108" s="16" t="s">
@@ -10555,7 +10555,7 @@
       <c r="G108" s="17" t="s">
         <v>706</v>
       </c>
-      <c r="H108" s="28"/>
+      <c r="H108" s="27"/>
     </row>
     <row r="109" spans="1:8" ht="66" customHeight="1">
       <c r="A109" s="16" t="s">
@@ -10579,7 +10579,7 @@
       <c r="G109" s="17" t="s">
         <v>712</v>
       </c>
-      <c r="H109" s="28"/>
+      <c r="H109" s="27"/>
     </row>
     <row r="110" spans="1:8" ht="66" customHeight="1">
       <c r="A110" s="16" t="s">
@@ -10603,7 +10603,7 @@
       <c r="G110" s="17" t="s">
         <v>720</v>
       </c>
-      <c r="H110" s="28"/>
+      <c r="H110" s="27"/>
     </row>
     <row r="111" spans="1:8" ht="66" customHeight="1">
       <c r="A111" s="16" t="s">
@@ -10627,7 +10627,7 @@
       <c r="G111" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="H111" s="28"/>
+      <c r="H111" s="27"/>
     </row>
     <row r="112" spans="1:8" ht="66" customHeight="1">
       <c r="A112" s="16" t="s">
@@ -10651,7 +10651,7 @@
       <c r="G112" s="17" t="s">
         <v>730</v>
       </c>
-      <c r="H112" s="28"/>
+      <c r="H112" s="27"/>
     </row>
     <row r="113" spans="1:8" ht="66" customHeight="1">
       <c r="A113" s="16" t="s">
@@ -10675,7 +10675,7 @@
       <c r="G113" s="17" t="s">
         <v>738</v>
       </c>
-      <c r="H113" s="28"/>
+      <c r="H113" s="27"/>
     </row>
     <row r="114" spans="1:8" ht="66" customHeight="1">
       <c r="A114" s="16" t="s">
@@ -10699,7 +10699,7 @@
       <c r="G114" s="17" t="s">
         <v>744</v>
       </c>
-      <c r="H114" s="28"/>
+      <c r="H114" s="27"/>
     </row>
     <row r="115" spans="1:8" ht="66" customHeight="1">
       <c r="A115" s="16" t="s">
@@ -10723,7 +10723,7 @@
       <c r="G115" s="17" t="s">
         <v>750</v>
       </c>
-      <c r="H115" s="28"/>
+      <c r="H115" s="27"/>
     </row>
     <row r="116" spans="1:8" ht="66" customHeight="1">
       <c r="A116" s="16" t="s">
@@ -10747,7 +10747,7 @@
       <c r="G116" s="17" t="s">
         <v>758</v>
       </c>
-      <c r="H116" s="28"/>
+      <c r="H116" s="27"/>
     </row>
     <row r="117" spans="1:8" ht="66" customHeight="1">
       <c r="A117" s="16" t="s">
@@ -10771,7 +10771,7 @@
       <c r="G117" s="17" t="s">
         <v>764</v>
       </c>
-      <c r="H117" s="28"/>
+      <c r="H117" s="27"/>
     </row>
     <row r="118" spans="1:8" ht="66" customHeight="1">
       <c r="A118" s="16" t="s">
@@ -10795,7 +10795,7 @@
       <c r="G118" s="17" t="s">
         <v>770</v>
       </c>
-      <c r="H118" s="28"/>
+      <c r="H118" s="27"/>
     </row>
     <row r="119" spans="1:8" ht="66" customHeight="1">
       <c r="A119" s="16" t="s">
@@ -10819,7 +10819,7 @@
       <c r="G119" s="17" t="s">
         <v>778</v>
       </c>
-      <c r="H119" s="28"/>
+      <c r="H119" s="27"/>
     </row>
     <row r="120" spans="1:8" ht="66" customHeight="1">
       <c r="A120" s="16" t="s">
@@ -10843,7 +10843,7 @@
       <c r="G120" s="17" t="s">
         <v>783</v>
       </c>
-      <c r="H120" s="28"/>
+      <c r="H120" s="27"/>
     </row>
     <row r="121" spans="1:8" ht="66" customHeight="1">
       <c r="A121" s="16" t="s">
@@ -10867,7 +10867,7 @@
       <c r="G121" s="17" t="s">
         <v>789</v>
       </c>
-      <c r="H121" s="28"/>
+      <c r="H121" s="27"/>
     </row>
     <row r="122" spans="1:8" ht="66" customHeight="1">
       <c r="A122" s="16" t="s">
@@ -10891,7 +10891,7 @@
       <c r="G122" s="17" t="s">
         <v>797</v>
       </c>
-      <c r="H122" s="28"/>
+      <c r="H122" s="27"/>
     </row>
     <row r="123" spans="1:8" ht="66" customHeight="1">
       <c r="A123" s="16" t="s">
@@ -10915,7 +10915,7 @@
       <c r="G123" s="17" t="s">
         <v>803</v>
       </c>
-      <c r="H123" s="28"/>
+      <c r="H123" s="27"/>
     </row>
     <row r="124" spans="1:8" ht="66" customHeight="1">
       <c r="A124" s="16" t="s">
@@ -10939,7 +10939,7 @@
       <c r="G124" s="17" t="s">
         <v>809</v>
       </c>
-      <c r="H124" s="28"/>
+      <c r="H124" s="27"/>
     </row>
     <row r="125" spans="1:8" ht="66" customHeight="1">
       <c r="A125" s="16" t="s">
@@ -10963,7 +10963,7 @@
       <c r="G125" s="17" t="s">
         <v>817</v>
       </c>
-      <c r="H125" s="28"/>
+      <c r="H125" s="27"/>
     </row>
     <row r="126" spans="1:8" ht="66" customHeight="1">
       <c r="A126" s="16" t="s">
@@ -10987,7 +10987,7 @@
       <c r="G126" s="17" t="s">
         <v>823</v>
       </c>
-      <c r="H126" s="28"/>
+      <c r="H126" s="27"/>
     </row>
     <row r="127" spans="1:8" ht="66" customHeight="1">
       <c r="A127" s="16" t="s">
@@ -11011,7 +11011,7 @@
       <c r="G127" s="17" t="s">
         <v>829</v>
       </c>
-      <c r="H127" s="28"/>
+      <c r="H127" s="27"/>
     </row>
     <row r="128" spans="1:8" ht="66" customHeight="1">
       <c r="A128" s="16" t="s">
@@ -11035,7 +11035,7 @@
       <c r="G128" s="17" t="s">
         <v>837</v>
       </c>
-      <c r="H128" s="28"/>
+      <c r="H128" s="27"/>
     </row>
     <row r="129" spans="1:8" ht="66" customHeight="1">
       <c r="A129" s="16" t="s">
@@ -11059,7 +11059,7 @@
       <c r="G129" s="17" t="s">
         <v>843</v>
       </c>
-      <c r="H129" s="28"/>
+      <c r="H129" s="27"/>
     </row>
     <row r="130" spans="1:8" ht="66" customHeight="1">
       <c r="A130" s="16" t="s">
@@ -11083,7 +11083,7 @@
       <c r="G130" s="17" t="s">
         <v>849</v>
       </c>
-      <c r="H130" s="28"/>
+      <c r="H130" s="27"/>
     </row>
     <row r="131" spans="1:8" ht="66" customHeight="1">
       <c r="A131" s="16" t="s">
@@ -11107,7 +11107,7 @@
       <c r="G131" s="17" t="s">
         <v>857</v>
       </c>
-      <c r="H131" s="28"/>
+      <c r="H131" s="27"/>
     </row>
     <row r="132" spans="1:8" ht="66" customHeight="1">
       <c r="A132" s="16" t="s">
@@ -11131,7 +11131,7 @@
       <c r="G132" s="17" t="s">
         <v>863</v>
       </c>
-      <c r="H132" s="28"/>
+      <c r="H132" s="27"/>
     </row>
     <row r="133" spans="1:8" ht="66" customHeight="1">
       <c r="A133" s="16" t="s">
@@ -11155,7 +11155,7 @@
       <c r="G133" s="17" t="s">
         <v>869</v>
       </c>
-      <c r="H133" s="28"/>
+      <c r="H133" s="27"/>
     </row>
     <row r="134" spans="1:8" ht="66" customHeight="1">
       <c r="A134" s="16" t="s">
@@ -11179,7 +11179,7 @@
       <c r="G134" s="17" t="s">
         <v>876</v>
       </c>
-      <c r="H134" s="28"/>
+      <c r="H134" s="27"/>
     </row>
     <row r="135" spans="1:8" ht="66" customHeight="1">
       <c r="A135" s="16" t="s">
@@ -11203,7 +11203,7 @@
       <c r="G135" s="17" t="s">
         <v>882</v>
       </c>
-      <c r="H135" s="28"/>
+      <c r="H135" s="27"/>
     </row>
     <row r="136" spans="1:8" ht="66" customHeight="1">
       <c r="A136" s="16" t="s">
@@ -11227,7 +11227,7 @@
       <c r="G136" s="17" t="s">
         <v>888</v>
       </c>
-      <c r="H136" s="28"/>
+      <c r="H136" s="27"/>
     </row>
     <row r="137" spans="1:8" ht="66" customHeight="1">
       <c r="A137" s="16" t="s">
@@ -11251,7 +11251,7 @@
       <c r="G137" s="17" t="s">
         <v>896</v>
       </c>
-      <c r="H137" s="28"/>
+      <c r="H137" s="27"/>
     </row>
     <row r="138" spans="1:8" ht="66" customHeight="1">
       <c r="A138" s="16" t="s">
@@ -11275,7 +11275,7 @@
       <c r="G138" s="17" t="s">
         <v>902</v>
       </c>
-      <c r="H138" s="28"/>
+      <c r="H138" s="27"/>
     </row>
     <row r="139" spans="1:8" ht="66" customHeight="1">
       <c r="A139" s="16" t="s">
@@ -11299,7 +11299,7 @@
       <c r="G139" s="17" t="s">
         <v>908</v>
       </c>
-      <c r="H139" s="28"/>
+      <c r="H139" s="27"/>
     </row>
     <row r="140" spans="1:8" ht="66" customHeight="1">
       <c r="A140" s="16" t="s">
@@ -11323,7 +11323,7 @@
       <c r="G140" s="17" t="s">
         <v>916</v>
       </c>
-      <c r="H140" s="28"/>
+      <c r="H140" s="27"/>
     </row>
     <row r="141" spans="1:8" ht="66" customHeight="1">
       <c r="A141" s="16" t="s">
@@ -11347,7 +11347,7 @@
       <c r="G141" s="17" t="s">
         <v>922</v>
       </c>
-      <c r="H141" s="28"/>
+      <c r="H141" s="27"/>
     </row>
     <row r="142" spans="1:8" ht="66" customHeight="1">
       <c r="A142" s="16" t="s">
@@ -11371,7 +11371,7 @@
       <c r="G142" s="17" t="s">
         <v>928</v>
       </c>
-      <c r="H142" s="28"/>
+      <c r="H142" s="27"/>
     </row>
     <row r="143" spans="1:8" ht="66" customHeight="1">
       <c r="A143" s="16" t="s">
@@ -11395,7 +11395,7 @@
       <c r="G143" s="17" t="s">
         <v>936</v>
       </c>
-      <c r="H143" s="28"/>
+      <c r="H143" s="27"/>
     </row>
     <row r="144" spans="1:8" ht="66" customHeight="1">
       <c r="A144" s="16" t="s">
@@ -11419,7 +11419,7 @@
       <c r="G144" s="17" t="s">
         <v>942</v>
       </c>
-      <c r="H144" s="28"/>
+      <c r="H144" s="27"/>
     </row>
     <row r="145" spans="1:8" ht="66" customHeight="1">
       <c r="A145" s="16" t="s">
@@ -11443,7 +11443,7 @@
       <c r="G145" s="17" t="s">
         <v>947</v>
       </c>
-      <c r="H145" s="29"/>
+      <c r="H145" s="28"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13063,12 +13063,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="30" t="s">
         <v>948</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
     </row>
     <row r="3" spans="1:4" ht="15">
       <c r="A3" s="7" t="s">
